--- a/artfynd/A 37901-2022 artfynd.xlsx
+++ b/artfynd/A 37901-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37901-2022 artfynd.xlsx
+++ b/artfynd/A 37901-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109610028</v>
+        <v>109610089</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569368.5547687454</v>
+        <v>569353</v>
       </c>
       <c r="R2" t="n">
-        <v>6377841.941349216</v>
+        <v>6377868</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>björkved</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109610089</v>
+        <v>109610071</v>
       </c>
       <c r="B3" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>306</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569353.5863817073</v>
+        <v>569529</v>
       </c>
       <c r="R3" t="n">
-        <v>6377867.992945896</v>
+        <v>6377759</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,21 +845,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -886,7 +861,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>björkved</t>
+          <t>aspved</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -904,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109610068</v>
+        <v>109610028</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569717.7945008166</v>
+        <v>569369</v>
       </c>
       <c r="R4" t="n">
-        <v>6377834.494303541</v>
+        <v>6377842</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,19 +947,9 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,6 +973,205 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>109610183</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80367</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Väderum, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>569627</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6377733</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pontus Axén, Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>109610068</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Väderum, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>569718</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6377834</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström, Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37901-2022 artfynd.xlsx
+++ b/artfynd/A 37901-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610089</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610071</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610028</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610183</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,8 +1197,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610068</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>